--- a/estadistica2/data/contreras_guzman.xlsx
+++ b/estadistica2/data/contreras_guzman.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096CE02C-F360-624D-9768-CBB26B59AF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1EFA50-A45A-3B4B-B0BA-E547C83D15D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -284,13 +284,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -310,22 +303,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -553,3113 +544,3090 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1000"/>
+  <dimension ref="A1:F966"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" style="4" customWidth="1"/>
-    <col min="2" max="4" width="10.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" style="4" customWidth="1"/>
-    <col min="7" max="28" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="2" customWidth="1"/>
+    <col min="2" max="4" width="10.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-    </row>
-    <row r="2" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
         <v>1.270532310009</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
         <v>58</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>5.38</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>0.82552284002304099</v>
       </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
         <v>48</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>20.7</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>0.45897394418716397</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
         <v>53</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>29.51</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>0.55132895708084095</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
         <v>45</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>30.44</v>
       </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>0.55335193872451804</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
         <v>41</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>32.590000000000003</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>0.82390129566192605</v>
       </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
         <v>51</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <v>38.15</v>
       </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>1.4733323454856899</v>
       </c>
-      <c r="B8" s="4">
-        <v>1</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
         <v>39</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>40.03</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>0.94717293977737405</v>
       </c>
-      <c r="B9" s="4">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
         <v>67</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>43.41</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>1.07130646705627</v>
       </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
         <v>53</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="8">
         <v>100</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>0.32599776983261097</v>
       </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
         <v>41</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>2.89</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>0.55288344621658303</v>
       </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4">
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
         <v>29</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="8">
         <v>3.44</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <v>1.1460974812507601</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
         <v>37</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <v>12.05</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <v>1.36777579784393</v>
       </c>
-      <c r="B14" s="4">
-        <v>1</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
         <v>33</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <v>15.55</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>9.1988146305084193</v>
       </c>
-      <c r="B15" s="4">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
         <v>39</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>2.5299999999999998</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>8.6344221234321594</v>
       </c>
-      <c r="B16" s="4">
-        <v>1</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
         <v>65</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="8">
         <v>4.24</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>0.80015242099761896</v>
       </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
         <v>60</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="8">
         <v>4.78</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>2.5774547457694998</v>
       </c>
-      <c r="B18" s="4">
-        <v>0</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
         <v>54</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="8">
         <v>5.68</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>2.3107111454010001</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
         <v>58</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <v>5.8</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>8.6308878660202009</v>
       </c>
-      <c r="B20" s="4">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
         <v>46</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="8">
         <v>6.06</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>1.0334992408752399</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2">
         <v>52</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <v>6.34</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>1.99143081903458</v>
       </c>
-      <c r="B22" s="4">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
         <v>30</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="8">
         <v>6.89</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>8.6643183231353706</v>
       </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="B23" s="2">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2">
         <v>54</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <v>7.71</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>7.4546906352043196</v>
       </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4">
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="8">
         <v>7.79</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>0.89784294366836603</v>
       </c>
-      <c r="B25" s="4">
-        <v>1</v>
-      </c>
-      <c r="C25" s="4">
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2">
         <v>36</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="8">
         <v>7.82</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>0.73778986930847201</v>
       </c>
-      <c r="B26" s="4">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4">
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2">
         <v>59</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <v>8.61</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <v>8.5237014293670708</v>
       </c>
-      <c r="B27" s="4">
-        <v>0</v>
-      </c>
-      <c r="C27" s="4">
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
         <v>25</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <v>9.9600000000000009</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <v>6.6965921223163596</v>
       </c>
-      <c r="B28" s="4">
-        <v>1</v>
-      </c>
-      <c r="C28" s="4">
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2">
         <v>51</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="8">
         <v>10.41</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>2.78713822364807</v>
       </c>
-      <c r="B29" s="4">
-        <v>0</v>
-      </c>
-      <c r="C29" s="4">
+      <c r="B29" s="2">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2">
         <v>49</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
         <v>11.38</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>3.2062311470508602</v>
       </c>
-      <c r="B30" s="4">
-        <v>0</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
         <v>30</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="8">
         <v>13.12</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>4.4510594010353097</v>
       </c>
-      <c r="B31" s="4">
-        <v>0</v>
-      </c>
-      <c r="C31" s="4">
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
         <v>44</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="8">
         <v>14.34</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>8.9737996459007299</v>
       </c>
-      <c r="B32" s="4">
-        <v>0</v>
-      </c>
-      <c r="C32" s="4">
+      <c r="B32" s="2">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
         <v>78</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="8">
         <v>19.350000000000001</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>0.73242396116256703</v>
       </c>
-      <c r="B33" s="4">
-        <v>0</v>
-      </c>
-      <c r="C33" s="4">
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
         <v>55</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="8">
         <v>2.54</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>2.3218637704849199</v>
       </c>
-      <c r="B34" s="4">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4">
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2">
         <v>58</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="8">
         <v>2.63</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>8.7934511899948102</v>
       </c>
-      <c r="B35" s="4">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4">
+      <c r="B35" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" s="2">
         <v>49</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="8">
         <v>3.5</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>2.94248700141907</v>
       </c>
-      <c r="B36" s="4">
-        <v>0</v>
-      </c>
-      <c r="C36" s="4">
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
         <v>32</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="10">
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="8">
         <v>3.53</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>3.6243911087513001</v>
       </c>
-      <c r="B37" s="4">
-        <v>0</v>
-      </c>
-      <c r="C37" s="4">
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
         <v>36</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="8">
         <v>3.75</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>8.8844913244247508</v>
       </c>
-      <c r="B38" s="4">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4">
+      <c r="B38" s="2">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2">
         <v>29</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="8">
         <v>3.84</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>1.99896961450577</v>
       </c>
-      <c r="B39" s="4">
-        <v>1</v>
-      </c>
-      <c r="C39" s="4">
+      <c r="B39" s="2">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2">
         <v>56</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="8">
         <v>4.24</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>0.78810751438140902</v>
       </c>
-      <c r="B40" s="4">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4">
+      <c r="B40" s="2">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2">
         <v>58</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="10">
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="8">
         <v>4.4800000000000004</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>4.1798034310340899</v>
       </c>
-      <c r="B41" s="4">
-        <v>0</v>
-      </c>
-      <c r="C41" s="4">
+      <c r="B41" s="2">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2">
         <v>67</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="8">
         <v>4.5</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>1.1344709992408799</v>
       </c>
-      <c r="B42" s="4">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4">
+      <c r="B42" s="2">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2">
         <v>39</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="8">
         <v>4.8</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>0.85048139095306396</v>
       </c>
-      <c r="B43" s="4">
-        <v>0</v>
-      </c>
-      <c r="C43" s="4">
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2">
         <v>48</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="8">
         <v>4.87</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>2.7597720921039599</v>
       </c>
-      <c r="B44" s="4">
-        <v>0</v>
-      </c>
-      <c r="C44" s="4">
+      <c r="B44" s="2">
+        <v>0</v>
+      </c>
+      <c r="C44" s="2">
         <v>32</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="10">
+      <c r="D44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="8">
         <v>4.87</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>2.83524557948112</v>
       </c>
-      <c r="B45" s="4">
-        <v>0</v>
-      </c>
-      <c r="C45" s="4">
+      <c r="B45" s="2">
+        <v>0</v>
+      </c>
+      <c r="C45" s="2">
         <v>24</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="10">
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="8">
         <v>4.92</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>6.7378564178943599</v>
       </c>
-      <c r="B46" s="4">
-        <v>1</v>
-      </c>
-      <c r="C46" s="4">
+      <c r="B46" s="2">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2">
         <v>33</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="8">
         <v>5.07</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47" s="2">
         <v>8.5253837704658508</v>
       </c>
-      <c r="B47" s="4">
-        <v>0</v>
-      </c>
-      <c r="C47" s="4">
+      <c r="B47" s="2">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2">
         <v>38</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="8">
         <v>5.44</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>3.3809244632721001</v>
       </c>
-      <c r="B48" s="4">
-        <v>0</v>
-      </c>
-      <c r="C48" s="4">
+      <c r="B48" s="2">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2">
         <v>37</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="8">
         <v>5.49</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>0.99864751100540206</v>
       </c>
-      <c r="B49" s="4">
-        <v>0</v>
-      </c>
-      <c r="C49" s="4">
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2">
         <v>54</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="8">
         <v>5.64</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="A50" s="2">
         <v>0.51383852958679199</v>
       </c>
-      <c r="B50" s="4">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4">
+      <c r="B50" s="2">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2">
         <v>36</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="8">
         <v>6.02</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
+      <c r="A51" s="2">
         <v>0.58638662099838301</v>
       </c>
-      <c r="B51" s="4">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4">
+      <c r="B51" s="2">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2">
         <v>33</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="10">
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="8">
         <v>6.59</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
+      <c r="A52" s="2">
         <v>0.94278931617736805</v>
       </c>
-      <c r="B52" s="4">
-        <v>1</v>
-      </c>
-      <c r="C52" s="4">
+      <c r="B52" s="2">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2">
         <v>41</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="8">
         <v>6.6</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
+      <c r="A53" s="2">
         <v>0.70146381855010997</v>
       </c>
-      <c r="B53" s="4">
-        <v>0</v>
-      </c>
-      <c r="C53" s="4">
+      <c r="B53" s="2">
+        <v>0</v>
+      </c>
+      <c r="C53" s="2">
         <v>65</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="10">
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="8">
         <v>6.66</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
+      <c r="A54" s="2">
         <v>0.56646913290023804</v>
       </c>
-      <c r="B54" s="4">
-        <v>1</v>
-      </c>
-      <c r="C54" s="4">
+      <c r="B54" s="2">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
         <v>64</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E54" s="8">
         <v>7.17</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
+      <c r="A55" s="2">
         <v>1.09455198049545</v>
       </c>
-      <c r="B55" s="4">
-        <v>0</v>
-      </c>
-      <c r="C55" s="4">
+      <c r="B55" s="2">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2">
         <v>33</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="8">
         <v>7.59</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>0.85150361061096203</v>
       </c>
-      <c r="B56" s="4">
-        <v>1</v>
-      </c>
-      <c r="C56" s="4">
+      <c r="B56" s="2">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2">
         <v>34</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="10">
+      <c r="D56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="8">
         <v>8.17</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
+      <c r="A57" s="2">
         <v>8.54080379009247</v>
       </c>
-      <c r="B57" s="4">
-        <v>0</v>
-      </c>
-      <c r="C57" s="4">
+      <c r="B57" s="2">
+        <v>0</v>
+      </c>
+      <c r="C57" s="2">
         <v>33</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="10">
+      <c r="E57" s="8">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>0.67867338657379195</v>
       </c>
-      <c r="B58" s="4">
-        <v>0</v>
-      </c>
-      <c r="C58" s="4">
+      <c r="B58" s="2">
+        <v>0</v>
+      </c>
+      <c r="C58" s="2">
         <v>37</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="10">
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="8">
         <v>8.41</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
+      <c r="A59" s="2">
         <v>0.88460683822631803</v>
       </c>
-      <c r="B59" s="4">
-        <v>1</v>
-      </c>
-      <c r="C59" s="4">
+      <c r="B59" s="2">
+        <v>1</v>
+      </c>
+      <c r="C59" s="2">
         <v>30</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="10">
+      <c r="D59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="8">
         <v>8.61</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>0.49916237592697099</v>
       </c>
-      <c r="B60" s="4">
-        <v>1</v>
-      </c>
-      <c r="C60" s="4">
+      <c r="B60" s="2">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2">
         <v>35</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="10">
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="8">
         <v>9.61</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
+      <c r="A61" s="2">
         <v>3.3145049214363098</v>
       </c>
-      <c r="B61" s="4">
-        <v>0</v>
-      </c>
-      <c r="C61" s="4">
+      <c r="B61" s="2">
+        <v>0</v>
+      </c>
+      <c r="C61" s="2">
         <v>33</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E61" s="10">
+      <c r="E61" s="8">
         <v>9.81</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>2.6822952926158901</v>
       </c>
-      <c r="B62" s="4">
-        <v>0</v>
-      </c>
-      <c r="C62" s="4">
+      <c r="B62" s="2">
+        <v>0</v>
+      </c>
+      <c r="C62" s="2">
         <v>56</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="10">
+      <c r="E62" s="8">
         <v>10.53</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
+      <c r="A63" s="2">
         <v>0.950583815574646</v>
       </c>
-      <c r="B63" s="4">
-        <v>1</v>
-      </c>
-      <c r="C63" s="4">
+      <c r="B63" s="2">
+        <v>1</v>
+      </c>
+      <c r="C63" s="2">
         <v>30</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="10">
+      <c r="D63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="8">
         <v>10.57</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
+      <c r="A64" s="2">
         <v>2.1907022595405601</v>
       </c>
-      <c r="B64" s="4">
-        <v>1</v>
-      </c>
-      <c r="C64" s="4">
+      <c r="B64" s="2">
+        <v>1</v>
+      </c>
+      <c r="C64" s="2">
         <v>54</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="10">
+      <c r="E64" s="8">
         <v>10.58</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
+      <c r="A65" s="2">
         <v>7.1173812448978397</v>
       </c>
-      <c r="B65" s="4">
-        <v>1</v>
-      </c>
-      <c r="C65" s="4">
+      <c r="B65" s="2">
+        <v>1</v>
+      </c>
+      <c r="C65" s="2">
         <v>34</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E65" s="10">
+      <c r="E65" s="8">
         <v>10.67</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>0.53918898105621305</v>
       </c>
-      <c r="B66" s="4">
-        <v>1</v>
-      </c>
-      <c r="C66" s="4">
+      <c r="B66" s="2">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2">
         <v>36</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="10">
+      <c r="E66" s="8">
         <v>12.32</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
+      <c r="A67" s="2">
         <v>1.5644174814224201</v>
       </c>
-      <c r="B67" s="4">
-        <v>1</v>
-      </c>
-      <c r="C67" s="4">
+      <c r="B67" s="2">
+        <v>1</v>
+      </c>
+      <c r="C67" s="2">
         <v>65</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E67" s="8">
         <v>12.65</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>0.83915680646896396</v>
       </c>
-      <c r="B68" s="4">
-        <v>1</v>
-      </c>
-      <c r="C68" s="4">
+      <c r="B68" s="2">
+        <v>1</v>
+      </c>
+      <c r="C68" s="2">
         <v>41</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="10">
+      <c r="D68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" s="8">
         <v>12.71</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="A69" s="2">
         <v>8.7813007831573504</v>
       </c>
-      <c r="B69" s="4">
-        <v>1</v>
-      </c>
-      <c r="C69" s="4">
+      <c r="B69" s="2">
+        <v>1</v>
+      </c>
+      <c r="C69" s="2">
         <v>52</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E69" s="10">
+      <c r="E69" s="8">
         <v>1.24</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
+      <c r="A70" s="2">
         <v>1.9163814187049899</v>
       </c>
-      <c r="B70" s="4">
-        <v>1</v>
-      </c>
-      <c r="C70" s="4">
+      <c r="B70" s="2">
+        <v>1</v>
+      </c>
+      <c r="C70" s="2">
         <v>31</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="8">
         <v>3.32</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
+      <c r="A71" s="2">
         <v>8.5119950771331805</v>
       </c>
-      <c r="B71" s="4">
-        <v>1</v>
-      </c>
-      <c r="C71" s="4">
+      <c r="B71" s="2">
+        <v>1</v>
+      </c>
+      <c r="C71" s="2">
         <v>67</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E71" s="10">
+      <c r="E71" s="8">
         <v>3.9</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>2.7929824590683001</v>
       </c>
-      <c r="B72" s="4">
-        <v>0</v>
-      </c>
-      <c r="C72" s="4">
+      <c r="B72" s="2">
+        <v>0</v>
+      </c>
+      <c r="C72" s="2">
         <v>32</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="10">
+      <c r="E72" s="8">
         <v>3.99</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
+      <c r="A73" s="2">
         <v>9.1212952136993408</v>
       </c>
-      <c r="B73" s="4">
-        <v>1</v>
-      </c>
-      <c r="C73" s="4">
+      <c r="B73" s="2">
+        <v>1</v>
+      </c>
+      <c r="C73" s="2">
         <v>42</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="10">
+      <c r="E73" s="8">
         <v>4.09</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
+      <c r="A74" s="2">
         <v>2.8748157620430002</v>
       </c>
-      <c r="B74" s="4">
-        <v>1</v>
-      </c>
-      <c r="C74" s="4">
+      <c r="B74" s="2">
+        <v>1</v>
+      </c>
+      <c r="C74" s="2">
         <v>40</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="10">
+      <c r="D74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="8">
         <v>4.46</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
+      <c r="A75" s="2">
         <v>0.85201412439346302</v>
       </c>
-      <c r="B75" s="4">
-        <v>0</v>
-      </c>
-      <c r="C75" s="4">
+      <c r="B75" s="2">
+        <v>0</v>
+      </c>
+      <c r="C75" s="2">
         <v>44</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="10">
+      <c r="D75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="8">
         <v>4.9000000000000004</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
+      <c r="A76" s="2">
         <v>2.4307882785797101</v>
       </c>
-      <c r="B76" s="4">
-        <v>1</v>
-      </c>
-      <c r="C76" s="4">
+      <c r="B76" s="2">
+        <v>1</v>
+      </c>
+      <c r="C76" s="2">
         <v>36</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="10">
+      <c r="D76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="8">
         <v>5.19</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4">
+      <c r="A77" s="2">
         <v>5.0061953667318404</v>
       </c>
-      <c r="B77" s="4">
-        <v>0</v>
-      </c>
-      <c r="C77" s="4">
+      <c r="B77" s="2">
+        <v>0</v>
+      </c>
+      <c r="C77" s="2">
         <v>48</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E77" s="10">
+      <c r="E77" s="8">
         <v>7.05</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>2.85266324877739</v>
       </c>
-      <c r="B78" s="4">
-        <v>0</v>
-      </c>
-      <c r="C78" s="4">
+      <c r="B78" s="2">
+        <v>0</v>
+      </c>
+      <c r="C78" s="2">
         <v>34</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E78" s="10">
+      <c r="E78" s="8">
         <v>7.28</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="4">
+      <c r="A79" s="2">
         <v>0.60072779655456598</v>
       </c>
-      <c r="B79" s="4">
-        <v>0</v>
-      </c>
-      <c r="C79" s="4">
+      <c r="B79" s="2">
+        <v>0</v>
+      </c>
+      <c r="C79" s="2">
         <v>31</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="10">
+      <c r="D79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="8">
         <v>8.85</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
+      <c r="A80" s="2">
         <v>0.96526443958282504</v>
       </c>
-      <c r="B80" s="4">
-        <v>1</v>
-      </c>
-      <c r="C80" s="4">
+      <c r="B80" s="2">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2">
         <v>41</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="10">
+      <c r="D80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="8">
         <v>9.42</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="4">
+      <c r="A81" s="2">
         <v>2.2306844592094399</v>
       </c>
-      <c r="B81" s="4">
-        <v>0</v>
-      </c>
-      <c r="C81" s="4">
+      <c r="B81" s="2">
+        <v>0</v>
+      </c>
+      <c r="C81" s="2">
         <v>41</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E81" s="10">
+      <c r="E81" s="8">
         <v>9.75</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
+      <c r="A82" s="2">
         <v>0.65803617238998402</v>
       </c>
-      <c r="B82" s="4">
-        <v>0</v>
-      </c>
-      <c r="C82" s="4">
+      <c r="B82" s="2">
+        <v>0</v>
+      </c>
+      <c r="C82" s="2">
         <v>37</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="10">
+      <c r="D82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="8">
         <v>10.28</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="4">
+      <c r="A83" s="2">
         <v>9.2073208093643206</v>
       </c>
-      <c r="B83" s="4">
-        <v>0</v>
-      </c>
-      <c r="C83" s="4">
+      <c r="B83" s="2">
+        <v>0</v>
+      </c>
+      <c r="C83" s="2">
         <v>42</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E83" s="10">
+      <c r="E83" s="8">
         <v>14.12</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>2.0628821849822998</v>
       </c>
-      <c r="B84" s="4">
-        <v>0</v>
-      </c>
-      <c r="C84" s="4">
+      <c r="B84" s="2">
+        <v>0</v>
+      </c>
+      <c r="C84" s="2">
         <v>25</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="10">
+      <c r="D84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="8">
         <v>0.73</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="4">
+      <c r="A85" s="2">
         <v>2.9265567660331699</v>
       </c>
-      <c r="B85" s="4">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4">
+      <c r="B85" s="2">
+        <v>1</v>
+      </c>
+      <c r="C85" s="2">
         <v>64</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="10">
+      <c r="D85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="8">
         <v>2.7</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="4">
+      <c r="A86" s="2">
         <v>7.0027497410774204</v>
       </c>
-      <c r="B86" s="4">
-        <v>1</v>
-      </c>
-      <c r="C86" s="4">
+      <c r="B86" s="2">
+        <v>1</v>
+      </c>
+      <c r="C86" s="2">
         <v>60</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E86" s="10">
+      <c r="E86" s="8">
         <v>3.02</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="4">
+      <c r="A87" s="2">
         <v>3.2703872025013001</v>
       </c>
-      <c r="B87" s="4">
-        <v>0</v>
-      </c>
-      <c r="C87" s="4">
+      <c r="B87" s="2">
+        <v>0</v>
+      </c>
+      <c r="C87" s="2">
         <v>32</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E87" s="10">
+      <c r="E87" s="8">
         <v>3.03</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="4">
+      <c r="A88" s="2">
         <v>3.4183989465236699</v>
       </c>
-      <c r="B88" s="4">
-        <v>0</v>
-      </c>
-      <c r="C88" s="4">
+      <c r="B88" s="2">
+        <v>0</v>
+      </c>
+      <c r="C88" s="2">
         <v>51</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="10">
+      <c r="E88" s="8">
         <v>3.09</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="4">
+      <c r="A89" s="2">
         <v>2.9724526405334499</v>
       </c>
-      <c r="B89" s="4">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4">
+      <c r="B89" s="2">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2">
         <v>47</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" s="10">
+      <c r="D89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" s="8">
         <v>3.42</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>4.24134328961373</v>
       </c>
-      <c r="B90" s="4">
-        <v>0</v>
-      </c>
-      <c r="C90" s="4">
+      <c r="B90" s="2">
+        <v>0</v>
+      </c>
+      <c r="C90" s="2">
         <v>70</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E90" s="10">
+      <c r="E90" s="8">
         <v>3.52</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="4">
+      <c r="A91" s="2">
         <v>6.9268320500850704</v>
       </c>
-      <c r="B91" s="4">
-        <v>0</v>
-      </c>
-      <c r="C91" s="4">
+      <c r="B91" s="2">
+        <v>0</v>
+      </c>
+      <c r="C91" s="2">
         <v>43</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E91" s="10">
+      <c r="E91" s="8">
         <v>3.55</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4">
+      <c r="A92" s="2">
         <v>8.7218740582466108</v>
       </c>
-      <c r="B92" s="4">
-        <v>0</v>
-      </c>
-      <c r="C92" s="4">
+      <c r="B92" s="2">
+        <v>0</v>
+      </c>
+      <c r="C92" s="2">
         <v>38</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E92" s="10">
+      <c r="E92" s="8">
         <v>3.65</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="4">
+      <c r="A93" s="2">
         <v>7.1280349791049904</v>
       </c>
-      <c r="B93" s="4">
-        <v>0</v>
-      </c>
-      <c r="C93" s="4">
+      <c r="B93" s="2">
+        <v>0</v>
+      </c>
+      <c r="C93" s="2">
         <v>33</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E93" s="10">
+      <c r="E93" s="8">
         <v>3.72</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="4">
+      <c r="A94" s="2">
         <v>7.2870290279388401</v>
       </c>
-      <c r="B94" s="4">
-        <v>0</v>
-      </c>
-      <c r="C94" s="4">
+      <c r="B94" s="2">
+        <v>0</v>
+      </c>
+      <c r="C94" s="2">
         <v>56</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E94" s="10">
+      <c r="E94" s="8">
         <v>4.3499999999999996</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="4">
+      <c r="A95" s="2">
         <v>3.3720007538795498</v>
       </c>
-      <c r="B95" s="4">
-        <v>1</v>
-      </c>
-      <c r="C95" s="4">
+      <c r="B95" s="2">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2">
         <v>34</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" s="10">
+      <c r="D95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="8">
         <v>4.46</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="4">
+      <c r="A96" s="2">
         <v>9.3626356124878001</v>
       </c>
-      <c r="B96" s="4">
-        <v>1</v>
-      </c>
-      <c r="C96" s="4">
+      <c r="B96" s="2">
+        <v>1</v>
+      </c>
+      <c r="C96" s="2">
         <v>35</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="10">
+      <c r="E96" s="8">
         <v>4.8899999999999997</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="4">
+      <c r="A97" s="2">
         <v>1.04410976171494</v>
       </c>
-      <c r="B97" s="4">
-        <v>0</v>
-      </c>
-      <c r="C97" s="4">
+      <c r="B97" s="2">
+        <v>0</v>
+      </c>
+      <c r="C97" s="2">
         <v>38</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97" s="10">
+      <c r="D97" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="8">
         <v>4.91</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="4">
+      <c r="A98" s="2">
         <v>0.83545953035354603</v>
       </c>
-      <c r="B98" s="4">
-        <v>1</v>
-      </c>
-      <c r="C98" s="4">
+      <c r="B98" s="2">
+        <v>1</v>
+      </c>
+      <c r="C98" s="2">
         <v>38</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="8">
         <v>5.31</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="4">
+      <c r="A99" s="2">
         <v>2.5735989212989798</v>
       </c>
-      <c r="B99" s="4">
-        <v>0</v>
-      </c>
-      <c r="C99" s="4">
+      <c r="B99" s="2">
+        <v>0</v>
+      </c>
+      <c r="C99" s="2">
         <v>75</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="10">
+      <c r="E99" s="8">
         <v>5.55</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="4">
+      <c r="A100" s="2">
         <v>2.4352112412452702</v>
       </c>
-      <c r="B100" s="4">
-        <v>1</v>
-      </c>
-      <c r="C100" s="4">
+      <c r="B100" s="2">
+        <v>1</v>
+      </c>
+      <c r="C100" s="2">
         <v>32</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="10">
+      <c r="E100" s="8">
         <v>5.6</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="4">
+      <c r="A101" s="2">
         <v>0.498128831386566</v>
       </c>
-      <c r="B101" s="4">
-        <v>1</v>
-      </c>
-      <c r="C101" s="4">
+      <c r="B101" s="2">
+        <v>1</v>
+      </c>
+      <c r="C101" s="2">
         <v>45</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E101" s="10">
+      <c r="D101" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="8">
         <v>5.64</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="4">
+      <c r="A102" s="2">
         <v>0.984316766262054</v>
       </c>
-      <c r="B102" s="4">
-        <v>1</v>
-      </c>
-      <c r="C102" s="4">
+      <c r="B102" s="2">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2">
         <v>35</v>
       </c>
-      <c r="D102" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E102" s="10">
+      <c r="D102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="8">
         <v>5.65</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="4">
+      <c r="A103" s="2">
         <v>0.466415286064148</v>
       </c>
-      <c r="B103" s="4">
-        <v>1</v>
-      </c>
-      <c r="C103" s="4">
+      <c r="B103" s="2">
+        <v>1</v>
+      </c>
+      <c r="C103" s="2">
         <v>43</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E103" s="10">
+      <c r="D103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="8">
         <v>5.68</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="4">
+      <c r="A104" s="2">
         <v>1.98984026908874</v>
       </c>
-      <c r="B104" s="4">
-        <v>1</v>
-      </c>
-      <c r="C104" s="4">
+      <c r="B104" s="2">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2">
         <v>40</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E104" s="10">
+      <c r="E104" s="8">
         <v>5.93</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="4">
+      <c r="A105" s="2">
         <v>0.94347059726715099</v>
       </c>
-      <c r="B105" s="4">
-        <v>1</v>
-      </c>
-      <c r="C105" s="4">
+      <c r="B105" s="2">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2">
         <v>29</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E105" s="10">
+      <c r="D105" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" s="8">
         <v>6.18</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="4">
+      <c r="A106" s="2">
         <v>2.4723342061042799</v>
       </c>
-      <c r="B106" s="4">
-        <v>1</v>
-      </c>
-      <c r="C106" s="4">
+      <c r="B106" s="2">
+        <v>1</v>
+      </c>
+      <c r="C106" s="2">
         <v>50</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E106" s="10">
+      <c r="E106" s="8">
         <v>7.59</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="4">
+      <c r="A107" s="2">
         <v>7.1917940676212302</v>
       </c>
-      <c r="B107" s="4">
-        <v>0</v>
-      </c>
-      <c r="C107" s="4">
+      <c r="B107" s="2">
+        <v>0</v>
+      </c>
+      <c r="C107" s="2">
         <v>46</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E107" s="10">
+      <c r="E107" s="8">
         <v>7.64</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="4">
+      <c r="A108" s="2">
         <v>1.83529496192932</v>
       </c>
-      <c r="B108" s="4">
-        <v>1</v>
-      </c>
-      <c r="C108" s="4">
+      <c r="B108" s="2">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2">
         <v>35</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="10">
+      <c r="E108" s="8">
         <v>7.85</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="4">
+      <c r="A109" s="2">
         <v>7.4384976923465702</v>
       </c>
-      <c r="B109" s="4">
-        <v>0</v>
-      </c>
-      <c r="C109" s="4">
+      <c r="B109" s="2">
+        <v>0</v>
+      </c>
+      <c r="C109" s="2">
         <v>68</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E109" s="10">
+      <c r="E109" s="8">
         <v>9.52</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="4">
+      <c r="A110" s="2">
         <v>0.52340298891067505</v>
       </c>
-      <c r="B110" s="4">
-        <v>1</v>
-      </c>
-      <c r="C110" s="4">
+      <c r="B110" s="2">
+        <v>1</v>
+      </c>
+      <c r="C110" s="2">
         <v>30</v>
       </c>
-      <c r="D110" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E110" s="10">
+      <c r="D110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="8">
         <v>9.98</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="4">
+      <c r="A111" s="2">
         <v>4.5350267365574801</v>
       </c>
-      <c r="B111" s="4">
-        <v>0</v>
-      </c>
-      <c r="C111" s="4">
+      <c r="B111" s="2">
+        <v>0</v>
+      </c>
+      <c r="C111" s="2">
         <v>41</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E111" s="10">
+      <c r="E111" s="8">
         <v>10.97</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="4">
+      <c r="A112" s="2">
         <v>1.93708151578903</v>
       </c>
-      <c r="B112" s="4">
-        <v>0</v>
-      </c>
-      <c r="C112" s="4">
+      <c r="B112" s="2">
+        <v>0</v>
+      </c>
+      <c r="C112" s="2">
         <v>62</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E112" s="10">
+      <c r="D112" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E112" s="8">
         <v>12.65</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="4">
+      <c r="A113" s="2">
         <v>9.1481310129165596</v>
       </c>
-      <c r="B113" s="4">
-        <v>1</v>
-      </c>
-      <c r="C113" s="4">
+      <c r="B113" s="2">
+        <v>1</v>
+      </c>
+      <c r="C113" s="2">
         <v>54</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E113" s="10">
+      <c r="E113" s="8">
         <v>21.85</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="4">
+      <c r="A114" s="2">
         <v>0.70087820291519198</v>
       </c>
-      <c r="B114" s="4">
-        <v>1</v>
-      </c>
-      <c r="C114" s="4">
+      <c r="B114" s="2">
+        <v>1</v>
+      </c>
+      <c r="C114" s="2">
         <v>47</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E114" s="10">
+      <c r="E114" s="8">
         <v>0.52</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="4">
+      <c r="A115" s="2">
         <v>2.5068888068199202</v>
       </c>
-      <c r="B115" s="4">
-        <v>1</v>
-      </c>
-      <c r="C115" s="4">
+      <c r="B115" s="2">
+        <v>1</v>
+      </c>
+      <c r="C115" s="2">
         <v>38</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E115" s="10">
+      <c r="E115" s="8">
         <v>0.79</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="4">
+      <c r="A116" s="2">
         <v>2.0770531892776498</v>
       </c>
-      <c r="B116" s="4">
-        <v>1</v>
-      </c>
-      <c r="C116" s="4">
+      <c r="B116" s="2">
+        <v>1</v>
+      </c>
+      <c r="C116" s="2">
         <v>34</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E116" s="10">
+      <c r="E116" s="8">
         <v>0.91</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="4">
+      <c r="A117" s="2">
         <v>2.1966788172721898</v>
       </c>
-      <c r="B117" s="4">
-        <v>1</v>
-      </c>
-      <c r="C117" s="4">
+      <c r="B117" s="2">
+        <v>1</v>
+      </c>
+      <c r="C117" s="2">
         <v>38</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E117" s="10">
+      <c r="E117" s="8">
         <v>0.98</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="4">
+      <c r="A118" s="2">
         <v>1.79888248443604</v>
       </c>
-      <c r="B118" s="4">
-        <v>1</v>
-      </c>
-      <c r="C118" s="4">
+      <c r="B118" s="2">
+        <v>1</v>
+      </c>
+      <c r="C118" s="2">
         <v>36</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E118" s="10">
+      <c r="E118" s="8">
         <v>2.12</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="4">
+      <c r="A119" s="2">
         <v>0.95171481370925903</v>
       </c>
-      <c r="B119" s="4">
-        <v>1</v>
-      </c>
-      <c r="C119" s="4">
+      <c r="B119" s="2">
+        <v>1</v>
+      </c>
+      <c r="C119" s="2">
         <v>21</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E119" s="10">
+      <c r="E119" s="8">
         <v>2.42</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="4">
+      <c r="A120" s="2">
         <v>0.48136442899704002</v>
       </c>
-      <c r="B120" s="4">
-        <v>0</v>
-      </c>
-      <c r="C120" s="4">
+      <c r="B120" s="2">
+        <v>0</v>
+      </c>
+      <c r="C120" s="2">
         <v>37</v>
       </c>
-      <c r="D120" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E120" s="10">
+      <c r="D120" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E120" s="8">
         <v>2.48</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="4">
+      <c r="A121" s="2">
         <v>6.3345716893672899</v>
       </c>
-      <c r="B121" s="4">
-        <v>0</v>
-      </c>
-      <c r="C121" s="4">
+      <c r="B121" s="2">
+        <v>0</v>
+      </c>
+      <c r="C121" s="2">
         <v>50</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E121" s="10">
+      <c r="E121" s="8">
         <v>3.04</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="4">
+      <c r="A122" s="2">
         <v>0.86343079805374201</v>
       </c>
-      <c r="B122" s="4">
-        <v>0</v>
-      </c>
-      <c r="C122" s="4">
+      <c r="B122" s="2">
+        <v>0</v>
+      </c>
+      <c r="C122" s="2">
         <v>30</v>
       </c>
-      <c r="D122" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E122" s="10">
+      <c r="D122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" s="8">
         <v>3.14</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="4">
+      <c r="A123" s="2">
         <v>0.57527720928192105</v>
       </c>
-      <c r="B123" s="4">
-        <v>1</v>
-      </c>
-      <c r="C123" s="4">
+      <c r="B123" s="2">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2">
         <v>46</v>
       </c>
-      <c r="D123" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E123" s="10">
+      <c r="D123" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="8">
         <v>3.23</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="4">
+      <c r="A124" s="2">
         <v>3.32156121730804</v>
       </c>
-      <c r="B124" s="4">
-        <v>1</v>
-      </c>
-      <c r="C124" s="4">
+      <c r="B124" s="2">
+        <v>1</v>
+      </c>
+      <c r="C124" s="2">
         <v>34</v>
       </c>
-      <c r="D124" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E124" s="10">
+      <c r="D124" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" s="8">
         <v>3.39</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="4">
+      <c r="A125" s="2">
         <v>3.7470199167728402</v>
       </c>
-      <c r="B125" s="4">
-        <v>0</v>
-      </c>
-      <c r="C125" s="4">
+      <c r="B125" s="2">
+        <v>0</v>
+      </c>
+      <c r="C125" s="2">
         <v>47</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D125" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E125" s="10">
+      <c r="E125" s="8">
         <v>3.58</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="4">
+      <c r="A126" s="2">
         <v>1.32567435503006</v>
       </c>
-      <c r="B126" s="4">
-        <v>1</v>
-      </c>
-      <c r="C126" s="4">
+      <c r="B126" s="2">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2">
         <v>51</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E126" s="10">
+      <c r="D126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" s="8">
         <v>3.77</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="4">
+      <c r="A127" s="2">
         <v>2.6994155347347299</v>
       </c>
-      <c r="B127" s="4">
-        <v>0</v>
-      </c>
-      <c r="C127" s="4">
+      <c r="B127" s="2">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2">
         <v>48</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D127" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E127" s="10">
+      <c r="E127" s="8">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="4">
+      <c r="A128" s="2">
         <v>1.08163297176361</v>
       </c>
-      <c r="B128" s="4">
-        <v>1</v>
-      </c>
-      <c r="C128" s="4">
+      <c r="B128" s="2">
+        <v>1</v>
+      </c>
+      <c r="C128" s="2">
         <v>63</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E128" s="10">
+      <c r="D128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E128" s="8">
         <v>4.13</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="4">
+      <c r="A129" s="2">
         <v>6.9920456409454301</v>
       </c>
-      <c r="B129" s="4">
-        <v>0</v>
-      </c>
-      <c r="C129" s="4">
+      <c r="B129" s="2">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2">
         <v>58</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="D129" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E129" s="10">
+      <c r="E129" s="8">
         <v>4.16</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="4">
+      <c r="A130" s="2">
         <v>6.6691660881042498</v>
       </c>
-      <c r="B130" s="4">
-        <v>0</v>
-      </c>
-      <c r="C130" s="4">
+      <c r="B130" s="2">
+        <v>0</v>
+      </c>
+      <c r="C130" s="2">
         <v>52</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E130" s="10">
+      <c r="E130" s="8">
         <v>4.3600000000000003</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="4">
+      <c r="A131" s="2">
         <v>0.45218557119369501</v>
       </c>
-      <c r="B131" s="4">
-        <v>0</v>
-      </c>
-      <c r="C131" s="4">
+      <c r="B131" s="2">
+        <v>0</v>
+      </c>
+      <c r="C131" s="2">
         <v>31</v>
       </c>
-      <c r="D131" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E131" s="10">
+      <c r="D131" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" s="8">
         <v>4.5</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="4">
+      <c r="A132" s="2">
         <v>0.43170630931854298</v>
       </c>
-      <c r="B132" s="4">
-        <v>1</v>
-      </c>
-      <c r="C132" s="4">
+      <c r="B132" s="2">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2">
         <v>49</v>
       </c>
-      <c r="D132" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E132" s="10">
+      <c r="D132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E132" s="8">
         <v>4.53</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="4">
+      <c r="A133" s="2">
         <v>8.5359621047973597</v>
       </c>
-      <c r="B133" s="4">
-        <v>0</v>
-      </c>
-      <c r="C133" s="4">
+      <c r="B133" s="2">
+        <v>0</v>
+      </c>
+      <c r="C133" s="2">
         <v>39</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E133" s="10">
+      <c r="E133" s="8">
         <v>4.9800000000000004</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="4">
+      <c r="A134" s="2">
         <v>2.4920099973678602</v>
       </c>
-      <c r="B134" s="4">
-        <v>0</v>
-      </c>
-      <c r="C134" s="4">
+      <c r="B134" s="2">
+        <v>0</v>
+      </c>
+      <c r="C134" s="2">
         <v>51</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E134" s="10">
+      <c r="E134" s="8">
         <v>5.15</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="4">
+      <c r="A135" s="2">
         <v>4.40698463469744</v>
       </c>
-      <c r="B135" s="4">
-        <v>0</v>
-      </c>
-      <c r="C135" s="4">
+      <c r="B135" s="2">
+        <v>0</v>
+      </c>
+      <c r="C135" s="2">
         <v>76</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E135" s="10">
+      <c r="E135" s="8">
         <v>5.35</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="4">
+      <c r="A136" s="2">
         <v>0.88893294334411599</v>
       </c>
-      <c r="B136" s="4">
-        <v>1</v>
-      </c>
-      <c r="C136" s="4">
+      <c r="B136" s="2">
+        <v>1</v>
+      </c>
+      <c r="C136" s="2">
         <v>39</v>
       </c>
-      <c r="D136" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E136" s="10">
+      <c r="D136" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="8">
         <v>5.49</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="4">
+      <c r="A137" s="2">
         <v>9.5600199699401909</v>
       </c>
-      <c r="B137" s="4">
-        <v>1</v>
-      </c>
-      <c r="C137" s="4">
+      <c r="B137" s="2">
+        <v>1</v>
+      </c>
+      <c r="C137" s="2">
         <v>42</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E137" s="10">
+      <c r="E137" s="8">
         <v>5.56</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="4">
+      <c r="A138" s="2">
         <v>0.53154468536376998</v>
       </c>
-      <c r="B138" s="4">
-        <v>1</v>
-      </c>
-      <c r="C138" s="4">
+      <c r="B138" s="2">
+        <v>1</v>
+      </c>
+      <c r="C138" s="2">
         <v>29</v>
       </c>
-      <c r="D138" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E138" s="10">
+      <c r="D138" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E138" s="8">
         <v>5.72</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="4">
+      <c r="A139" s="2">
         <v>2.1108382940292398</v>
       </c>
-      <c r="B139" s="4">
-        <v>1</v>
-      </c>
-      <c r="C139" s="4">
+      <c r="B139" s="2">
+        <v>1</v>
+      </c>
+      <c r="C139" s="2">
         <v>50</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="D139" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E139" s="10">
+      <c r="E139" s="8">
         <v>6.05</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="4">
+      <c r="A140" s="2">
         <v>5.5579743161797497</v>
       </c>
-      <c r="B140" s="4">
-        <v>0</v>
-      </c>
-      <c r="C140" s="4">
+      <c r="B140" s="2">
+        <v>0</v>
+      </c>
+      <c r="C140" s="2">
         <v>75</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E140" s="10">
+      <c r="E140" s="8">
         <v>6.29</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="4">
+      <c r="A141" s="2">
         <v>8.5126641392707807</v>
       </c>
-      <c r="B141" s="4">
-        <v>0</v>
-      </c>
-      <c r="C141" s="4">
+      <c r="B141" s="2">
+        <v>0</v>
+      </c>
+      <c r="C141" s="2">
         <v>81</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E141" s="10">
+      <c r="E141" s="8">
         <v>6.49</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="4">
+      <c r="A142" s="2">
         <v>3.2135401666164398</v>
       </c>
-      <c r="B142" s="4">
-        <v>1</v>
-      </c>
-      <c r="C142" s="4">
+      <c r="B142" s="2">
+        <v>1</v>
+      </c>
+      <c r="C142" s="2">
         <v>69</v>
       </c>
-      <c r="D142" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E142" s="10">
+      <c r="D142" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142" s="8">
         <v>7.47</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="4">
+      <c r="A143" s="2">
         <v>7.2938536107540104</v>
       </c>
-      <c r="B143" s="4">
-        <v>1</v>
-      </c>
-      <c r="C143" s="4">
+      <c r="B143" s="2">
+        <v>1</v>
+      </c>
+      <c r="C143" s="2">
         <v>48</v>
       </c>
-      <c r="D143" s="4" t="s">
+      <c r="D143" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E143" s="10">
+      <c r="E143" s="8">
         <v>7.94</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="4">
+      <c r="A144" s="2">
         <v>9.4806435704231298</v>
       </c>
-      <c r="B144" s="4">
-        <v>1</v>
-      </c>
-      <c r="C144" s="4">
+      <c r="B144" s="2">
+        <v>1</v>
+      </c>
+      <c r="C144" s="2">
         <v>48</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E144" s="10">
+      <c r="E144" s="8">
         <v>9.5299999999999994</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="4">
+      <c r="A145" s="2">
         <v>1.55009061098099</v>
       </c>
-      <c r="B145" s="4">
-        <v>0</v>
-      </c>
-      <c r="C145" s="4">
+      <c r="B145" s="2">
+        <v>0</v>
+      </c>
+      <c r="C145" s="2">
         <v>74</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E145" s="10">
+      <c r="E145" s="8">
         <v>10.3</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="4">
+      <c r="A146" s="2">
         <v>3.3547639846801798</v>
       </c>
-      <c r="B146" s="4">
-        <v>0</v>
-      </c>
-      <c r="C146" s="4">
+      <c r="B146" s="2">
+        <v>0</v>
+      </c>
+      <c r="C146" s="2">
         <v>52</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="D146" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E146" s="10">
+      <c r="E146" s="8">
         <v>12.36</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="4">
+      <c r="A147" s="2">
         <v>2.4845197796821599</v>
       </c>
-      <c r="B147" s="4">
-        <v>0</v>
-      </c>
-      <c r="C147" s="4">
+      <c r="B147" s="2">
+        <v>0</v>
+      </c>
+      <c r="C147" s="2">
         <v>44</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E147" s="10">
+      <c r="E147" s="8">
         <v>13.12</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="4">
+      <c r="A148" s="2">
         <v>2.2935831546783501</v>
       </c>
-      <c r="B148" s="4">
-        <v>0</v>
-      </c>
-      <c r="C148" s="4">
+      <c r="B148" s="2">
+        <v>0</v>
+      </c>
+      <c r="C148" s="2">
         <v>55</v>
       </c>
-      <c r="D148" s="4" t="s">
+      <c r="D148" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E148" s="10">
+      <c r="E148" s="8">
         <v>24.65</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="4">
+      <c r="A149" s="2">
         <v>4.3371690809726697</v>
       </c>
-      <c r="B149" s="4">
-        <v>0</v>
-      </c>
-      <c r="C149" s="4">
+      <c r="B149" s="2">
+        <v>0</v>
+      </c>
+      <c r="C149" s="2">
         <v>52</v>
       </c>
-      <c r="D149" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E149" s="10">
+      <c r="D149" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E149" s="8">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="4">
+      <c r="A150" s="2">
         <v>0.50843179225921598</v>
       </c>
-      <c r="B150" s="4">
-        <v>0</v>
-      </c>
-      <c r="C150" s="4">
+      <c r="B150" s="2">
+        <v>0</v>
+      </c>
+      <c r="C150" s="2">
         <v>32</v>
       </c>
-      <c r="D150" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E150" s="10">
+      <c r="D150" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E150" s="8">
         <v>2.06</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="4">
+      <c r="A151" s="2">
         <v>2.45162010192871</v>
       </c>
-      <c r="B151" s="4">
-        <v>0</v>
-      </c>
-      <c r="C151" s="4">
+      <c r="B151" s="2">
+        <v>0</v>
+      </c>
+      <c r="C151" s="2">
         <v>41</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E151" s="10">
+      <c r="E151" s="8">
         <v>2.5</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="4">
+      <c r="A152" s="2">
         <v>0.92325001955032404</v>
       </c>
-      <c r="B152" s="4">
-        <v>1</v>
-      </c>
-      <c r="C152" s="4">
+      <c r="B152" s="2">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2">
         <v>31</v>
       </c>
-      <c r="D152" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E152" s="10">
+      <c r="D152" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E152" s="8">
         <v>2.65</v>
       </c>
-      <c r="F152" s="4">
+      <c r="F152" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="4">
+      <c r="A153" s="2">
         <v>7.2523204982280696</v>
       </c>
-      <c r="B153" s="4">
-        <v>0</v>
-      </c>
-      <c r="C153" s="4">
+      <c r="B153" s="2">
+        <v>0</v>
+      </c>
+      <c r="C153" s="2">
         <v>34</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="D153" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E153" s="10">
+      <c r="E153" s="8">
         <v>3.29</v>
       </c>
-      <c r="F153" s="4">
+      <c r="F153" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="4">
+      <c r="A154" s="2">
         <v>0.57149112224578902</v>
       </c>
-      <c r="B154" s="4">
-        <v>1</v>
-      </c>
-      <c r="C154" s="4">
+      <c r="B154" s="2">
+        <v>1</v>
+      </c>
+      <c r="C154" s="2">
         <v>28</v>
       </c>
-      <c r="D154" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E154" s="10">
+      <c r="D154" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E154" s="8">
         <v>3.46</v>
       </c>
-      <c r="F154" s="4">
+      <c r="F154" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="4">
+      <c r="A155" s="2">
         <v>1.82164371013641</v>
       </c>
-      <c r="B155" s="4">
-        <v>1</v>
-      </c>
-      <c r="C155" s="4">
+      <c r="B155" s="2">
+        <v>1</v>
+      </c>
+      <c r="C155" s="2">
         <v>40</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E155" s="10">
+      <c r="E155" s="8">
         <v>3.61</v>
       </c>
-      <c r="F155" s="4">
+      <c r="F155" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="4">
+      <c r="A156" s="2">
         <v>0.73643267154693604</v>
       </c>
-      <c r="B156" s="4">
-        <v>1</v>
-      </c>
-      <c r="C156" s="4">
+      <c r="B156" s="2">
+        <v>1</v>
+      </c>
+      <c r="C156" s="2">
         <v>36</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E156" s="10">
+      <c r="E156" s="8">
         <v>5.82</v>
       </c>
-      <c r="F156" s="4">
+      <c r="F156" s="2">
         <v>8</v>
       </c>
     </row>
@@ -4473,43 +4441,9 @@
     <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1003">
-    <sortCondition ref="F1:F1003"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F969">
+    <sortCondition ref="F1:F969"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -4528,100 +4462,100 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>52</v>
       </c>
     </row>

--- a/estadistica2/data/contreras_guzman.xlsx
+++ b/estadistica2/data/contreras_guzman.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A630AC-F0A8-7244-A15E-4BC460DCD4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63697B9-F0F2-B34E-B198-6F5A881EB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="54">
   <si>
     <t>coord1D_normal_all</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>1 a 8</t>
+  </si>
+  <si>
+    <t>izquierda_derecha</t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>

--- a/estadistica2/data/contreras_guzman.xlsx
+++ b/estadistica2/data/contreras_guzman.xlsx
@@ -2,22 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63697B9-F0F2-B34E-B198-6F5A881EB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA12A83-84BC-A244-BCAB-E914DAB5F692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="680" yWindow="940" windowWidth="27640" windowHeight="15940" xr2:uid="{D9DB2D0C-ACCD-B84C-8A66-61C17E195879}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="4" r:id="rId1"/>
-    <sheet name="Codebook" sheetId="2" r:id="rId2"/>
-    <sheet name="Variable" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,9 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="33">
   <si>
-    <t>coord1D_normal_all</t>
+    <t>izquierda_derecha</t>
   </si>
   <si>
     <t>sexo</t>
@@ -56,19 +56,43 @@
     <t>magnitud_distrital</t>
   </si>
   <si>
+    <t>PC-IND</t>
+  </si>
+  <si>
     <t>PPD-IND</t>
+  </si>
+  <si>
+    <t>RN-IND</t>
+  </si>
+  <si>
+    <t>UDI-IND</t>
   </si>
   <si>
     <t>IND</t>
   </si>
   <si>
-    <t>UDI-IND</t>
+    <t>PL-IND</t>
   </si>
   <si>
-    <t>IFP</t>
+    <t xml:space="preserve">PS </t>
   </si>
   <si>
     <t>PC</t>
+  </si>
+  <si>
+    <t>RD-IND</t>
+  </si>
+  <si>
+    <t>UDI</t>
+  </si>
+  <si>
+    <t>RN</t>
+  </si>
+  <si>
+    <t>EVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC </t>
   </si>
   <si>
     <t>FRVS</t>
@@ -77,127 +101,40 @@
     <t>PS-IND</t>
   </si>
   <si>
-    <t xml:space="preserve">PS </t>
+    <t>CS-IND</t>
   </si>
   <si>
-    <t>UDI</t>
+    <t xml:space="preserve">PPD </t>
   </si>
   <si>
-    <t>PC-IND</t>
+    <t>PR-IND</t>
   </si>
   <si>
-    <t>RN</t>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>PI-IND</t>
+  </si>
+  <si>
+    <t>IFP</t>
+  </si>
+  <si>
+    <t>RD</t>
   </si>
   <si>
     <t>PRO-IND</t>
   </si>
   <si>
-    <t>RD-IND</t>
+    <t>DC-IND</t>
+  </si>
+  <si>
+    <t>EVO-IND</t>
   </si>
   <si>
     <t>FRVS-IND</t>
   </si>
   <si>
-    <t>PL-IND</t>
-  </si>
-  <si>
-    <t>RN-IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPD </t>
-  </si>
-  <si>
     <t>COM-IND</t>
-  </si>
-  <si>
-    <t>CS-IND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC </t>
-  </si>
-  <si>
-    <t>RD</t>
-  </si>
-  <si>
-    <t>PR-IND</t>
-  </si>
-  <si>
-    <t>EVO</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>EVO-IND</t>
-  </si>
-  <si>
-    <t>PI-IND</t>
-  </si>
-  <si>
-    <t>DC-IND</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Izquierda derecha (0-10)</t>
-  </si>
-  <si>
-    <t>Masculino=0 / femenino=1</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de variable </t>
-  </si>
-  <si>
-    <t>Continua</t>
-  </si>
-  <si>
-    <t>Nominal</t>
-  </si>
-  <si>
-    <t>Discreta</t>
-  </si>
-  <si>
-    <t>Edad del canditado</t>
-  </si>
-  <si>
-    <t>Partido politico</t>
-  </si>
-  <si>
-    <t>Porcentaje de votos obtenidos por el cantidato</t>
-  </si>
-  <si>
-    <t>Número de escaños asigandos en el distrito</t>
-  </si>
-  <si>
-    <t>Categórica (binaria)</t>
-  </si>
-  <si>
-    <t>Escala</t>
-  </si>
-  <si>
-    <t>Sexo del canditado</t>
-  </si>
-  <si>
-    <t>21 - 81</t>
-  </si>
-  <si>
-    <t>0 - 10</t>
-  </si>
-  <si>
-    <t>PS, RN, IND, UDI, PC, PPD-IND, IFP, FRVS, PRO-IND, RD-IND, COM-IND, CS-IND, EVO, RD, PL, PI-IND, DC, CS, PS-IND</t>
-  </si>
-  <si>
-    <t>0,52 - 100</t>
-  </si>
-  <si>
-    <t>1 a 8</t>
-  </si>
-  <si>
-    <t>izquierda_derecha</t>
   </si>
 </sst>
 </file>
@@ -207,8 +144,9 @@
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,21 +157,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -241,32 +173,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -286,20 +198,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
@@ -323,19 +235,113 @@
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Narrow"/>
-        <a:ea typeface="Aptos Narrow"/>
-        <a:cs typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
-        <a:ea typeface="Aptos Narrow"/>
-        <a:cs typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,13 +403,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -412,6 +411,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -476,41 +482,58 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A29A180-DE8B-E64E-A6A2-D41B81B9CD86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950889D6-4DF3-8246-819D-3B4DC95648A7}">
   <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -559,7 +582,7 @@
         <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>29.51</v>
@@ -647,7 +670,7 @@
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>43.41</v>
@@ -752,7 +775,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2.5299999999999998</v>
@@ -772,7 +795,7 @@
         <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>4.24</v>
@@ -792,7 +815,7 @@
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>4.78</v>
@@ -812,7 +835,7 @@
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <v>5.68</v>
@@ -832,7 +855,7 @@
         <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19">
         <v>5.8</v>
@@ -852,7 +875,7 @@
         <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>6.06</v>
@@ -872,7 +895,7 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E21">
         <v>6.34</v>
@@ -892,7 +915,7 @@
         <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>6.89</v>
@@ -912,7 +935,7 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>7.71</v>
@@ -952,7 +975,7 @@
         <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>7.82</v>
@@ -972,7 +995,7 @@
         <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26">
         <v>8.61</v>
@@ -992,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>9.9600000000000009</v>
@@ -1012,7 +1035,7 @@
         <v>51</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E28">
         <v>10.41</v>
@@ -1032,7 +1055,7 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E29">
         <v>11.38</v>
@@ -1052,7 +1075,7 @@
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30">
         <v>13.12</v>
@@ -1072,7 +1095,7 @@
         <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>14.34</v>
@@ -1112,7 +1135,7 @@
         <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>2.54</v>
@@ -1132,7 +1155,7 @@
         <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E34">
         <v>2.63</v>
@@ -1152,7 +1175,7 @@
         <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>3.5</v>
@@ -1172,7 +1195,7 @@
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>3.53</v>
@@ -1192,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37">
         <v>3.75</v>
@@ -1212,7 +1235,7 @@
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>3.84</v>
@@ -1232,7 +1255,7 @@
         <v>56</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <v>4.24</v>
@@ -1252,7 +1275,7 @@
         <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E40">
         <v>4.4800000000000004</v>
@@ -1272,7 +1295,7 @@
         <v>67</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41">
         <v>4.5</v>
@@ -1292,7 +1315,7 @@
         <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E42">
         <v>4.8</v>
@@ -1312,7 +1335,7 @@
         <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E43">
         <v>4.87</v>
@@ -1332,7 +1355,7 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E44">
         <v>4.87</v>
@@ -1352,7 +1375,7 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>4.92</v>
@@ -1392,7 +1415,7 @@
         <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>5.44</v>
@@ -1412,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48">
         <v>5.49</v>
@@ -1466,7 +1489,7 @@
         <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E51">
         <v>6.59</v>
@@ -1486,7 +1509,7 @@
         <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E52">
         <v>6.6</v>
@@ -1506,7 +1529,7 @@
         <v>65</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53">
         <v>6.66</v>
@@ -1543,7 +1566,7 @@
         <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E55">
         <v>7.59</v>
@@ -1563,7 +1586,7 @@
         <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E56">
         <v>8.17</v>
@@ -1583,7 +1606,7 @@
         <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57">
         <v>8.2899999999999991</v>
@@ -1603,7 +1626,7 @@
         <v>37</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E58">
         <v>8.41</v>
@@ -1623,7 +1646,7 @@
         <v>30</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E59">
         <v>8.61</v>
@@ -1643,7 +1666,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E60">
         <v>9.61</v>
@@ -1663,7 +1686,7 @@
         <v>33</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61">
         <v>9.81</v>
@@ -1683,7 +1706,7 @@
         <v>56</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62">
         <v>10.53</v>
@@ -1703,7 +1726,7 @@
         <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E63">
         <v>10.57</v>
@@ -1723,7 +1746,7 @@
         <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E64">
         <v>10.58</v>
@@ -1763,7 +1786,7 @@
         <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E66">
         <v>12.32</v>
@@ -1783,7 +1806,7 @@
         <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E67">
         <v>12.65</v>
@@ -1803,7 +1826,7 @@
         <v>41</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E68">
         <v>12.71</v>
@@ -1823,7 +1846,7 @@
         <v>52</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E69">
         <v>1.24</v>
@@ -1843,7 +1866,7 @@
         <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E70">
         <v>3.32</v>
@@ -1863,7 +1886,7 @@
         <v>67</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E71">
         <v>3.9</v>
@@ -1883,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E72">
         <v>3.99</v>
@@ -1903,7 +1926,7 @@
         <v>42</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E73">
         <v>4.09</v>
@@ -1923,7 +1946,7 @@
         <v>40</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E74">
         <v>4.46</v>
@@ -1943,7 +1966,7 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E75">
         <v>4.9000000000000004</v>
@@ -1963,7 +1986,7 @@
         <v>36</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E76">
         <v>5.19</v>
@@ -2003,7 +2026,7 @@
         <v>34</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E78">
         <v>7.28</v>
@@ -2023,7 +2046,7 @@
         <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E79">
         <v>8.85</v>
@@ -2043,7 +2066,7 @@
         <v>41</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E80">
         <v>9.42</v>
@@ -2063,7 +2086,7 @@
         <v>41</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E81">
         <v>9.75</v>
@@ -2083,7 +2106,7 @@
         <v>37</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E82">
         <v>10.28</v>
@@ -2103,7 +2126,7 @@
         <v>42</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E83">
         <v>14.12</v>
@@ -2123,7 +2146,7 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E84">
         <v>0.73</v>
@@ -2143,7 +2166,7 @@
         <v>64</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E85">
         <v>2.7</v>
@@ -2163,7 +2186,7 @@
         <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E86">
         <v>3.02</v>
@@ -2183,7 +2206,7 @@
         <v>32</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E87">
         <v>3.03</v>
@@ -2203,7 +2226,7 @@
         <v>51</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E88">
         <v>3.09</v>
@@ -2223,7 +2246,7 @@
         <v>47</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E89">
         <v>3.42</v>
@@ -2283,7 +2306,7 @@
         <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E92">
         <v>3.65</v>
@@ -2303,7 +2326,7 @@
         <v>33</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E93">
         <v>3.72</v>
@@ -2323,7 +2346,7 @@
         <v>56</v>
       </c>
       <c r="D94" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E94">
         <v>4.3499999999999996</v>
@@ -2343,7 +2366,7 @@
         <v>34</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>4.46</v>
@@ -2363,7 +2386,7 @@
         <v>35</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E96">
         <v>4.8899999999999997</v>
@@ -2383,7 +2406,7 @@
         <v>38</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E97">
         <v>4.91</v>
@@ -2403,7 +2426,7 @@
         <v>38</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E98">
         <v>5.31</v>
@@ -2423,7 +2446,7 @@
         <v>75</v>
       </c>
       <c r="D99" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E99">
         <v>5.55</v>
@@ -2443,7 +2466,7 @@
         <v>32</v>
       </c>
       <c r="D100" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E100">
         <v>5.6</v>
@@ -2463,7 +2486,7 @@
         <v>45</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E101">
         <v>5.64</v>
@@ -2483,7 +2506,7 @@
         <v>35</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102">
         <v>5.65</v>
@@ -2503,7 +2526,7 @@
         <v>43</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E103">
         <v>5.68</v>
@@ -2523,7 +2546,7 @@
         <v>40</v>
       </c>
       <c r="D104" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E104">
         <v>5.93</v>
@@ -2543,7 +2566,7 @@
         <v>29</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E105">
         <v>6.18</v>
@@ -2563,7 +2586,7 @@
         <v>50</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E106">
         <v>7.59</v>
@@ -2583,7 +2606,7 @@
         <v>46</v>
       </c>
       <c r="D107" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E107">
         <v>7.64</v>
@@ -2603,7 +2626,7 @@
         <v>35</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E108">
         <v>7.85</v>
@@ -2643,7 +2666,7 @@
         <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E110">
         <v>9.98</v>
@@ -2663,7 +2686,7 @@
         <v>41</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E111">
         <v>10.97</v>
@@ -2683,7 +2706,7 @@
         <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E112">
         <v>12.65</v>
@@ -2703,7 +2726,7 @@
         <v>54</v>
       </c>
       <c r="D113" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113">
         <v>21.85</v>
@@ -2723,7 +2746,7 @@
         <v>47</v>
       </c>
       <c r="D114" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E114">
         <v>0.52</v>
@@ -2743,7 +2766,7 @@
         <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E115">
         <v>0.79</v>
@@ -2763,7 +2786,7 @@
         <v>34</v>
       </c>
       <c r="D116" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E116">
         <v>0.91</v>
@@ -2783,7 +2806,7 @@
         <v>38</v>
       </c>
       <c r="D117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E117">
         <v>0.98</v>
@@ -2803,7 +2826,7 @@
         <v>36</v>
       </c>
       <c r="D118" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E118">
         <v>2.12</v>
@@ -2823,7 +2846,7 @@
         <v>21</v>
       </c>
       <c r="D119" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E119">
         <v>2.42</v>
@@ -2843,7 +2866,7 @@
         <v>37</v>
       </c>
       <c r="D120" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E120">
         <v>2.48</v>
@@ -2883,7 +2906,7 @@
         <v>30</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E122">
         <v>3.14</v>
@@ -2903,7 +2926,7 @@
         <v>46</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E123">
         <v>3.23</v>
@@ -2923,7 +2946,7 @@
         <v>34</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E124">
         <v>3.39</v>
@@ -2943,7 +2966,7 @@
         <v>47</v>
       </c>
       <c r="D125" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E125">
         <v>3.58</v>
@@ -2963,7 +2986,7 @@
         <v>51</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E126">
         <v>3.77</v>
@@ -2983,7 +3006,7 @@
         <v>48</v>
       </c>
       <c r="D127" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E127">
         <v>4.0199999999999996</v>
@@ -3003,7 +3026,7 @@
         <v>63</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E128">
         <v>4.13</v>
@@ -3063,7 +3086,7 @@
         <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E131">
         <v>4.5</v>
@@ -3083,7 +3106,7 @@
         <v>49</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132">
         <v>4.53</v>
@@ -3103,7 +3126,7 @@
         <v>39</v>
       </c>
       <c r="D133" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E133">
         <v>4.9800000000000004</v>
@@ -3123,7 +3146,7 @@
         <v>51</v>
       </c>
       <c r="D134" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E134">
         <v>5.15</v>
@@ -3143,7 +3166,7 @@
         <v>76</v>
       </c>
       <c r="D135" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E135">
         <v>5.35</v>
@@ -3163,7 +3186,7 @@
         <v>39</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E136">
         <v>5.49</v>
@@ -3203,7 +3226,7 @@
         <v>29</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E138">
         <v>5.72</v>
@@ -3223,7 +3246,7 @@
         <v>50</v>
       </c>
       <c r="D139" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E139">
         <v>6.05</v>
@@ -3263,7 +3286,7 @@
         <v>81</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E141">
         <v>6.49</v>
@@ -3283,7 +3306,7 @@
         <v>69</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E142">
         <v>7.47</v>
@@ -3323,7 +3346,7 @@
         <v>48</v>
       </c>
       <c r="D144" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E144">
         <v>9.5299999999999994</v>
@@ -3343,7 +3366,7 @@
         <v>74</v>
       </c>
       <c r="D145" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E145">
         <v>10.3</v>
@@ -3363,7 +3386,7 @@
         <v>52</v>
       </c>
       <c r="D146" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E146">
         <v>12.36</v>
@@ -3383,7 +3406,7 @@
         <v>44</v>
       </c>
       <c r="D147" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E147">
         <v>13.12</v>
@@ -3403,7 +3426,7 @@
         <v>55</v>
       </c>
       <c r="D148" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E148">
         <v>24.65</v>
@@ -3423,7 +3446,7 @@
         <v>52</v>
       </c>
       <c r="D149" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E149">
         <v>1.1499999999999999</v>
@@ -3443,7 +3466,7 @@
         <v>32</v>
       </c>
       <c r="D150" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E150">
         <v>2.06</v>
@@ -3463,7 +3486,7 @@
         <v>41</v>
       </c>
       <c r="D151" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E151">
         <v>2.5</v>
@@ -3483,7 +3506,7 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E152">
         <v>2.65</v>
@@ -3503,7 +3526,7 @@
         <v>34</v>
       </c>
       <c r="D153" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E153">
         <v>3.29</v>
@@ -3523,7 +3546,7 @@
         <v>28</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E154">
         <v>3.46</v>
@@ -3543,7 +3566,7 @@
         <v>40</v>
       </c>
       <c r="D155" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E155">
         <v>3.61</v>
@@ -3563,7 +3586,7 @@
         <v>36</v>
       </c>
       <c r="D156" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E156">
         <v>5.82</v>
@@ -3575,128 +3598,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFEF01C1-56FA-4CC4-A7AF-F967E94C503F}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="37.5" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="31.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22F61D67-A817-4FA8-9E31-498BEE94FCFC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>